--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/03_Repositoryverzeichnis.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/03_Repositoryverzeichnis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repositories" sheetId="1" r:id="Rbc24073b8b004282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domains_Marken_Doku" sheetId="2" r:id="R4b202a184bc74270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zugriff_Export" sheetId="3" r:id="R77c669d7a60c4edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repositories" sheetId="1" r:id="R1da31a418cbb4c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domains_Marken_Doku" sheetId="2" r:id="R6455f6c6deb14fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zugriff_Export" sheetId="3" r:id="Ra639014b05684366"/>
   </x:sheets>
 </x:workbook>
 </file>
